--- a/Outputs/Scenarios/PtX_demand_FR_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_FR_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.006379959808676661</v>
       </c>
       <c r="K16" t="n">
-        <v>0.006320500214814401</v>
+        <v>0.007716057101497999</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.001335227694788333</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0126410004296288</v>
+        <v>0.01068182155830667</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0.0005112911688710039</v>
       </c>
       <c r="K24" t="n">
-        <v>0.009096149444370493</v>
+        <v>0.009096149444370491</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.00309484652084073</v>
       </c>
       <c r="K25" t="n">
-        <v>0.08532557299497318</v>
+        <v>0.08532557299497316</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>9.192442138230554e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.002106833404938134</v>
+        <v>0.001335227694788333</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.009444753759612115</v>
       </c>
       <c r="K30" t="n">
-        <v>0.03382513997362099</v>
+        <v>0.04129367971396962</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.007145678686476698</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.06765027994724197</v>
+        <v>0.05716542949181359</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0004970923031374797</v>
       </c>
       <c r="K42" t="n">
-        <v>0.01127504665787366</v>
+        <v>0.007145678686476698</v>
       </c>
     </row>
     <row r="43">
